--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2052,6 +2052,107 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125796790</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91220</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>569259</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7011731</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>125796790</v>
       </c>
       <c r="B13" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>125796790</v>
       </c>
       <c r="B13" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>125796790</v>
       </c>
       <c r="B13" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>125796790</v>
       </c>
       <c r="B13" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>125796790</v>
       </c>
       <c r="B13" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>125796790</v>
       </c>
       <c r="B13" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>125796790</v>
       </c>
       <c r="B13" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>125796790</v>
       </c>
       <c r="B13" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56357335</v>
+        <v>103997250</v>
       </c>
       <c r="B2" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569283.9080485839</v>
+        <v>569015</v>
       </c>
       <c r="R2" t="n">
-        <v>7011883.720606419</v>
+        <v>7012092</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-21</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-21</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,47 +767,34 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gammal, oliiåldrig tallskog på torr moränmark</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal ratad tallstock</t>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56357333</v>
+        <v>56357331</v>
       </c>
       <c r="B3" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569114.6777005085</v>
+        <v>569199</v>
       </c>
       <c r="R3" t="n">
-        <v>7011920.674738571</v>
+        <v>7011738</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,21 +859,11 @@
           <t>2015-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-09-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,15 +875,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>gammal, olikåldrig tallskog på torr moränmark</t>
+          <t>160-årig tallskog på moränmark med lingon</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # gamla brända tallågor</t>
+          <t>5 substratenheter # gamla brända tallågerester</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,12 +908,7 @@
         <v>56357332</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569097.536452901</v>
+        <v>569098</v>
       </c>
       <c r="R4" t="n">
-        <v>7011835.526777173</v>
+        <v>7011836</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,19 +973,9 @@
           <t>2015-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,12 +1022,7 @@
         <v>56357334</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569283.9080485839</v>
+        <v>569284</v>
       </c>
       <c r="R5" t="n">
-        <v>7011883.720606419</v>
+        <v>7011884</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,19 +1087,9 @@
           <t>2015-09-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,15 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56357331</v>
+        <v>103997259</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,37 +1144,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569198.986670166</v>
+        <v>569245</v>
       </c>
       <c r="R6" t="n">
-        <v>7011737.586303206</v>
+        <v>7011738</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,22 +1198,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-09-21</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-09-21</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,47 +1225,34 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>160-årig tallskog på moränmark med lingon</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>5 substratenheter # gamla brända tallågerester</t>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103997192</v>
+        <v>125796790</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1360,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569254.6878677807</v>
+        <v>569259</v>
       </c>
       <c r="R7" t="n">
-        <v>7011751.409616647</v>
+        <v>7011731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1390,22 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,62 +1330,52 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103997250</v>
+        <v>103997210</v>
       </c>
       <c r="B8" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>306</v>
+        <v>1460</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569014.3711175029</v>
+        <v>569036</v>
       </c>
       <c r="R8" t="n">
-        <v>7012092.138832391</v>
+        <v>7012101</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1562,15 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103997243</v>
+        <v>56357333</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,37 +1477,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Pikhöjden, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569038.6372896413</v>
+        <v>569115</v>
       </c>
       <c r="R9" t="n">
-        <v>7012097.618605031</v>
+        <v>7011921</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1632,22 +1531,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2015-09-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2015-09-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,39 +1548,42 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>gammal, olikåldrig tallskog på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>2 substratenheter # gamla brända tallågor</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103997259</v>
+        <v>56357335</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,37 +1591,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Pikhöjden, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569245.0380715042</v>
+        <v>569284</v>
       </c>
       <c r="R10" t="n">
-        <v>7011738.123950757</v>
+        <v>7011884</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1753,22 +1645,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2015-09-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2015-09-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,39 +1662,42 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>gammal, oliiåldrig tallskog på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal ratad tallstock</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103997210</v>
+        <v>103997246</v>
       </c>
       <c r="B11" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1460</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1844,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569035.3910547546</v>
+        <v>569174</v>
       </c>
       <c r="R11" t="n">
-        <v>7012101.607453892</v>
+        <v>7011872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1879,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1889,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,55 +1810,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103997203</v>
+        <v>103997208</v>
       </c>
       <c r="B12" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102204</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569108.1038540197</v>
+        <v>569137</v>
       </c>
       <c r="R12" t="n">
-        <v>7011658.518610393</v>
+        <v>7011635</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2005,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2015,21 +1890,15 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spår i tunn grankvist</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2057,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125796790</v>
+        <v>103997177</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,21 +1937,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2092,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569259</v>
+        <v>569144</v>
       </c>
       <c r="R13" t="n">
-        <v>7011731</v>
+        <v>7011645</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2122,12 +1991,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2138,21 +2017,385 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>103997192</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>569255</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7011752</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103997243</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>569038</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7012098</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103997203</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>569108</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7011659</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spår i tunn grankvist</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 41406-2023 artfynd.xlsx
+++ b/artfynd/A 41406-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357331</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357332</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357334</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997259</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796790</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997210</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357333</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1691,6 +1736,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357335</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997246</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1923,6 +1978,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997208</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2039,6 +2099,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997177</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2155,6 +2220,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997192</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2271,6 +2341,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997243</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2398,8 +2473,30 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997203</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>